--- a/RFID Tag/v0.1/BOM.xlsx
+++ b/RFID Tag/v0.1/BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/dstjohn_email_sc_edu/Documents/Desktop/rfid-tire-sensor-tag/system_development/hardware/tag/v0.1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/dstjohn_email_sc_edu/Documents/Desktop/Smart-Tire/RFID Tag/v0.1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{8455079B-1614-4F03-A1A0-8D4A44D52A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFB7763D-4152-46D9-A0DE-21F0732C2833}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{8455079B-1614-4F03-A1A0-8D4A44D52A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DEEA50C-7174-4884-AB26-B44C90EAE2A3}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-2190" windowWidth="29040" windowHeight="15720" xr2:uid="{7B1818A1-D48D-4A2D-937D-1A40A73D14FA}"/>
   </bookViews>
@@ -82,27 +82,6 @@
     <t>Sensor Sweep</t>
   </si>
   <si>
-    <t>47 pF Â±5% 50V C0G/NP0 Ceramic Cap (Lower Sweep)</t>
-  </si>
-  <si>
-    <t>YAGEO CC0603JPNPO0BN470</t>
-  </si>
-  <si>
-    <t>13-CC0603JPNPO0BN470CT-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.digikey.com/en/products/detail/yageo/CC0603JPNPO0BN470/11490751 </t>
-  </si>
-  <si>
-    <t>56 pF Â±5% 50V C0G/NP0 Ceramic Cap (Upper Sweep)</t>
-  </si>
-  <si>
-    <t>YAGEO CC0603JRNPOYBN560</t>
-  </si>
-  <si>
-    <t>13-CC0603JRNPOYBN560CT-ND</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -127,9 +106,6 @@
     <t xml:space="preserve">https://www.digikey.com/en/products/detail/m5stack-technology-co-ltd/U107/14318610?s=N4IgTCBcDa5mBGAtAVQQBgOxIHIBEQBdAXyA </t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.digikey.com/en/products/detail/yageo/CC0603JRNPOYBN560/11489919  </t>
-  </si>
-  <si>
     <t>RFID Tag Traces</t>
   </si>
   <si>
@@ -140,6 +116,30 @@
   </si>
   <si>
     <t xml:space="preserve">https://store.voltera.io/products/conductor-4-silver-nanoparticle-ink?variant=48526802321630 </t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/w-rth-elektronik/885012006077/9345852</t>
+  </si>
+  <si>
+    <t>732-12040-2-ND</t>
+  </si>
+  <si>
+    <t>Wurth Elektronik 885012006077</t>
+  </si>
+  <si>
+    <t>CAP CER 47PF 100V C0G/NP0 0603</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/murata-electronics/GQM1875C2E560GB12D/3900470</t>
+  </si>
+  <si>
+    <t>490-7174-2-ND</t>
+  </si>
+  <si>
+    <t>Murata GQM1875C2E560GB12D</t>
+  </si>
+  <si>
+    <t>CAP CER 56PF 250V C0G/NP0 0603</t>
   </si>
 </sst>
 </file>
@@ -1108,13 +1108,13 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>603</v>
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1134,13 +1134,13 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F5">
         <v>603</v>
@@ -1149,7 +1149,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>2</v>
@@ -1169,7 +1169,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>6</v>
@@ -1180,25 +1180,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>2</v>
@@ -1218,7 +1218,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>6</v>
@@ -1229,35 +1229,33 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{FF9D33C9-6546-415B-9891-3A187B7F5F73}"/>
     <hyperlink ref="H8" r:id="rId2" xr:uid="{8FF7BBBC-A857-4F74-9744-6AA5E9BFA491}"/>
-    <hyperlink ref="H5" r:id="rId3" xr:uid="{291DC7B3-C963-47C9-A6CC-DA1C8CB833DF}"/>
-    <hyperlink ref="H11" r:id="rId4" xr:uid="{C575DD65-2F80-4037-A1A0-B66EC983D610}"/>
-    <hyperlink ref="H3" r:id="rId5" xr:uid="{9EE1F397-2D0C-4D33-B5A6-1FB6E6526B96}"/>
-    <hyperlink ref="H4" r:id="rId6" xr:uid="{17842812-9234-455E-AD87-5C21C27658FA}"/>
+    <hyperlink ref="H11" r:id="rId3" xr:uid="{C575DD65-2F80-4037-A1A0-B66EC983D610}"/>
+    <hyperlink ref="H3" r:id="rId4" xr:uid="{9EE1F397-2D0C-4D33-B5A6-1FB6E6526B96}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
